--- a/Trắc nghiệm ôn luyện/Tester Technical/multiple_choice_sample_template_API_TESTING.xlsx
+++ b/Trắc nghiệm ôn luyện/Tester Technical/multiple_choice_sample_template_API_TESTING.xlsx
@@ -447,7 +447,7 @@
         <v>Khi thực hiện kiểm thử API (API Testing), mã trạng thái phản hồi HTTP (HTTP Status Code) nào biểu thị yêu cầu đã được xử lý thành công?</v>
       </c>
       <c r="C2" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D2" t="str">
         <v>Đầu mã 2xx đại diện cho thành công, trong đó 200 OK là mã phản hồi chuẩn nhất cho các API truy vấn thành công.</v>
@@ -476,7 +476,7 @@
         <v>Trong kiểm thử API, phương thức HTTP Method nào thường được dùng để tạo mới một đối tượng dữ liệu?</v>
       </c>
       <c r="C3" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D3" t="str">
         <v>POST là phương thức chuẩn theo kiến trúc RESTful dùng để tạo mới các thực thể/dữ liệu trên hệ thống máy chủ.</v>
@@ -505,7 +505,7 @@
         <v>Mã phản hồi HTTP Status Code 403 Forbidden biểu thị điều gì khi gọi một API?</v>
       </c>
       <c r="C4" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D4" t="str">
         <v>403 Forbidden nghĩa là server hiểu yêu cầu nhưng từ chối thực hiện vì tài khoản hiện tại không được cấp quyền truy cập.</v>
@@ -534,7 +534,7 @@
         <v>Trong kiểm thử tự động (Automation Testing), từ khóa "Locator" dùng để làm gì?</v>
       </c>
       <c r="C5" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D5" t="str">
         <v>Locator (bộ định vị) giúp script tự động biết cần click vào nút nào, nhập chữ vào ô nào bằng cách quét cấu trúc DOM của trang web.</v>
@@ -563,7 +563,7 @@
         <v>Khi chạy test API bằng công cụ Postman, tab "Tests" dùng để thực hiện công việc gì?</v>
       </c>
       <c r="C6" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D6" t="str">
         <v>Tab Tests trong Postman cho phép QA viết script Assertions bằng JS để tự động hóa việc kiểm tra tính đúng đắn của dữ liệu API trả về.</v>
@@ -592,7 +592,7 @@
         <v>Trong kiểm thử tự động trang web (Web Automation), bộ định vị (Locator) nào sau đây có tốc độ tìm kiếm nhanh nhất và độ tin cậy cao nhất?</v>
       </c>
       <c r="C7" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D7" t="str">
         <v>Tìm kiếm phần tử bằng ID luôn nhanh nhất và ổn định nhất vì ID được thiết kế là duy nhất trên trang, giúp script không bị nhận nhầm phần tử.</v>
@@ -621,7 +621,7 @@
         <v>Trong kiểm thử tự động, công cụ Selenium WebDriver đóng vai trò gì?</v>
       </c>
       <c r="C8" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D8" t="str">
         <v>Selenium WebDriver đóng vai trò trung gian nhận lệnh từ script test và dịch thành các hành động điều khiển native trên trình duyệt web.</v>
@@ -650,7 +650,7 @@
         <v>Khi gọi API để cập nhật một phần dữ liệu của bản ghi (ví dụ: Chỉ cập nhật số điện thoại của tài khoản), phương thức HTTP nào phù hợp nhất?</v>
       </c>
       <c r="C9" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D9" t="str">
         <v>Theo chuẩn RESTful, PATCH dùng cho cập nhật cục bộ một số trường, trong khi PUT dùng để thay thế toàn bộ tài nguyên cũ bằng tài nguyên mới.</v>
@@ -679,7 +679,7 @@
         <v>Mã phản hồi HTTP Status Code 401 Unauthorized và 403 Forbidden khác nhau ở điểm cốt lõi nào?</v>
       </c>
       <c r="C10" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D10" t="str">
         <v>401 (Authentication) yêu cầu xác định "Bạn là ai?". 403 (Authorization) kiểm tra "Bạn có quyền thực hiện việc này không?".</v>
@@ -708,7 +708,7 @@
         <v>Khi viết script Selenium để tìm một button trên trang web có cấu trúc DOM động (id thay đổi mỗi lần reload), QA nên dùng chiến lược định vị nào?</v>
       </c>
       <c r="C11" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D11" t="str">
         <v>Với phần tử động, QA sử dụng XPath tương đối, so khớp chuỗi con (`contains`) hoặc tìm theo quan hệ cha-con (relative XPath) để đảm bảo script chạy ổn định.</v>
@@ -737,7 +737,7 @@
         <v>Khái niệm "Implicit Wait" và "Explicit Wait" trong Selenium WebDriver khác nhau như thế nào?</v>
       </c>
       <c r="C12" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D12" t="str">
         <v>Implicit Wait cấu hình chung (global). Explicit Wait thông minh hơn, chỉ kích hoạt khi cần thiết (ví dụ: Chờ nút hiển thị rõ để click - ExpectedConditions) giúp giảm flaky test.</v>
@@ -766,7 +766,7 @@
         <v>Khi thực hiện kiểm thử tự động bằng mô hình Page Object Model (POM), lợi ích lớn nhất thu được là gì?</v>
       </c>
       <c r="C13" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D13" t="str">
         <v>POM đóng gói các phần tử và hành vi của một trang web vào một Class. Khi giao diện đổi (ví dụ đổi ID của nút), QA chỉ cần sửa Locator trong Class Page đó, không phải sửa hàng chục Test script.</v>
@@ -795,7 +795,7 @@
         <v>Trong Postman, khi cần truyền token bảo mật (Bearer Token) thu được từ API Đăng nhập sang các API tiếp theo một cách tự động, QA thực hiện thế nào?</v>
       </c>
       <c r="C14" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D14" t="str">
         <v>Sử dụng biến môi trường (e.g. `pm.environment.set("token", pm.response.json().token)`) giúp tự động hóa hoàn toàn chuỗi API test chain.</v>
@@ -824,7 +824,7 @@
         <v>Khi chạy kiểm thử tự động trên trình duyệt, lỗi "StaleElementReferenceException" trong Selenium nghĩa là gì?</v>
       </c>
       <c r="C15" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D15" t="str">
         <v>Lỗi này xảy ra khi tham chiếu đến một đối tượng DOM đã cũ (stale). Khắc phục bằng cách tìm lại phần tử đó (find element lại) trước khi thực hiện hành động tiếp theo.</v>
@@ -853,7 +853,7 @@
         <v>Sự khác biệt chính về mặt kiến trúc giữa SOAP API và REST API khi thực hiện kiểm thử API là gì?</v>
       </c>
       <c r="C16" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D16" t="str">
         <v>SOAP là giao thức đặc tả chặt chẽ dựa trên XML. REST là phong cách kiến trúc nhẹ nhàng, dễ sử dụng, được ứng dụng rộng rãi trong các ứng dụng web/mobile hiện đại.</v>
@@ -882,7 +882,7 @@
         <v>Trong kiểm thử tự động, kỹ thuật "Data-driven Testing" (Kiểm thử hướng dữ liệu) giải quyết bài toán nào?</v>
       </c>
       <c r="C17" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D17" t="str">
         <v>Data-driven testing giúp tăng độ bao phủ. Thay vì viết 10 test case riêng biệt cho 10 tài khoản, ta chỉ viết 1 script và nạp 10 dòng tài khoản từ file CSV vào.</v>
@@ -911,7 +911,7 @@
         <v>Khi viết bộ lọc XPath, sự khác biệt giữa `/` (single slash) và `//` (double slash) là gì?</v>
       </c>
       <c r="C18" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D18" t="str">
         <v>`/` đi tuần tự từ gốc (root node). `//` thực hiện tìm kiếm tương đối trên toàn bộ cây DOM bên dưới từ vị trí hiện tại.</v>
@@ -940,7 +940,7 @@
         <v>Bạn gọi API POST để tạo sản phẩm mới. Response trả về mã 201 Created kèm JSON payload nhưng DB không lưu được dữ liệu mới. Lỗi thuộc về thành phần nào và QA báo cáo thế nào?</v>
       </c>
       <c r="C19" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D19" t="str">
         <v>Status code 201 đại diện cho việc tạo tài nguyên thành công. Nếu DB không có, BE đã trả code láo (không bắt exception từ DB hoặc transaction bị rollback). Đây là lỗi logic Backend.</v>
@@ -969,7 +969,7 @@
         <v>Khi chạy CI/CD, script automation web báo lỗi: "ElementClickInterceptedException: Element is not clickable at point... Other element would receive the click". QA xử lý lỗi này thế nào?</v>
       </c>
       <c r="C20" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D20" t="str">
         <v>Lỗi này do phần tử bị che bởi một phần tử khác (như spinner, popup quảng cáo). Cách sạch nhất là chờ spinner biến mất, hoặc dùng JS click `arguments[0].click();` để tác động thẳng vào DOM.</v>
@@ -998,7 +998,7 @@
         <v>Đặc tả API quy định: Khi gửi request GET /products?id=ABC (trong đó id kiểu integer), API phải trả về lỗi 400 Bad Request. Thực tế gọi API trả về 500 Internal Server Error kèm SQL exception log. Lỗi này chỉ ra vấn đề gì?</v>
       </c>
       <c r="C21" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D21" t="str">
         <v>Hệ thống cần validate kiểu dữ liệu ở tầng API/Controller và trả về lỗi 4xx rõ ràng. Việc trả về lỗi 500 kèm SQL dump chứng tỏ BE để lọt dữ liệu bẩn xuống DB, gây nguy cơ bảo mật nghiêm trọng.</v>
@@ -1027,7 +1027,7 @@
         <v>Khi thiết kế framework kiểm thử tự động cho một trang thương mại điện tử lớn, tại sao nên kết hợp Page Object Model (POM) và Factory Pattern?</v>
       </c>
       <c r="C22" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D22" t="str">
         <v>Factory Pattern giúp quản lý việc tạo đối tượng Page. Khi chuyển trang, Factory tự động sinh ra Page Object tiếp theo tương ứng, giữ cho mã nguồn script gọn gàng và dễ mở rộng.</v>
@@ -1056,7 +1056,7 @@
         <v>Để kiểm thử API của một ứng dụng tài chính dưới điều kiện bảo mật cao, QA cần thực hiện kịch bản kiểm thử bảo mật cơ bản nào đối với JWT (JSON Web Token)?</v>
       </c>
       <c r="C23" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D23" t="str">
         <v>Cả hai kịch bản (Signature manipulation và Algorithm None attack) là các lỗ hổng kinh điển của JWT. Việc kiểm thử này giúp bảo vệ hệ thống trước các cuộc tấn công giả mạo danh tính.</v>
@@ -1085,7 +1085,7 @@
         <v>Khi thực hiện kiểm thử tự động chạy song song (Parallel Execution) trên nhiều luồng để giảm thời gian test, QA gặp hiện tượng các test case bị xung đột dữ liệu (data conflict). Giải pháp xử lý là gì?</v>
       </c>
       <c r="C24" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D24" t="str">
         <v>Chạy song song yêu cầu các test case không được dùng chung dữ liệu tĩnh (như dùng chung một tài khoản VIP để sửa thông tin cùng lúc). Thiết kế dữ liệu cô lập (Isolate) là nguyên tắc sống còn.</v>
@@ -1114,7 +1114,7 @@
         <v>Trong Postman, làm thế nào để validate một API Response trả về khớp hoàn toàn với một JSON Schema định sẵn để kiểm tra kiểu dữ liệu của các trường?</v>
       </c>
       <c r="C25" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D25" t="str">
         <v>Sử dụng AJV giúp QA validate toàn bộ cấu trúc response (kiểu dữ liệu, các trường bắt buộc, min/max length) chỉ bằng một đoạn code ngắn, đảm bảo API không bị đổi cấu trúc đột ngột.</v>
@@ -1143,7 +1143,7 @@
         <v>Khi chạy automation test trên mobile bằng Appium, tại sao việc quản lý ứng dụng nền (background apps) và trạng thái kết nối mạng lại phức tạp hơn so với web, và QA giải quyết thế nào?</v>
       </c>
       <c r="C26" t="str">
-        <v>Tester Technical</v>
+        <v>Tester API Testing</v>
       </c>
       <c r="D26" t="str">
         <v>Appium cung cấp các API tương tác với phần cứng thiết bị (giả lập mất mạng, đẩy app vào nền rồi mở lại) giúp QA bao phủ các kịch bản sử dụng thực tế phức tạp của mobile app.</v>

--- a/Trắc nghiệm ôn luyện/Tester Technical/multiple_choice_sample_template_API_TESTING.xlsx
+++ b/Trắc nghiệm ôn luyện/Tester Technical/multiple_choice_sample_template_API_TESTING.xlsx
@@ -453,19 +453,19 @@
         <v>Đầu mã 2xx đại diện cho thành công, trong đó 200 OK là mã phản hồi chuẩn nhất cho các API truy vấn thành công.</v>
       </c>
       <c r="E2" t="str">
+        <v>400 Bad Request — yêu cầu gửi đi bị sai cú pháp hoặc thiếu tham số bắt buộc</v>
+      </c>
+      <c r="F2" t="str">
+        <v>401 Unauthorized — yêu cầu chưa được xác thực tài khoản đăng nhập</v>
+      </c>
+      <c r="G2" t="str">
+        <v>500 Internal Server Error — lỗi hệ thống phát sinh ở máy chủ ứng dụng</v>
+      </c>
+      <c r="H2" t="str">
         <v>200 OK — yêu cầu được xử lý thành công và trả về dữ liệu tương ứng</v>
       </c>
-      <c r="F2" t="str">
-        <v>400 Bad Request — yêu cầu gửi đi bị sai cú pháp hoặc thiếu tham số bắt buộc</v>
-      </c>
-      <c r="G2" t="str">
-        <v>401 Unauthorized — yêu cầu chưa được xác thực tài khoản đăng nhập</v>
-      </c>
-      <c r="H2" t="str">
-        <v>500 Internal Server Error — lỗi hệ thống phát sinh ở máy chủ ứng dụng</v>
-      </c>
       <c r="I2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -482,19 +482,19 @@
         <v>POST là phương thức chuẩn theo kiến trúc RESTful dùng để tạo mới các thực thể/dữ liệu trên hệ thống máy chủ.</v>
       </c>
       <c r="E3" t="str">
+        <v>DELETE — xóa bỏ bản ghi dữ liệu khỏi hệ thống</v>
+      </c>
+      <c r="F3" t="str">
         <v>POST — gửi dữ liệu lên server để tạo mới bản ghi</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>GET — gửi yêu cầu truy vấn lấy dữ liệu từ server về</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>PUT — cập nhật lại thông tin của toàn bộ bản ghi hiện có</v>
       </c>
-      <c r="H3" t="str">
-        <v>DELETE — xóa bỏ bản ghi dữ liệu khỏi hệ thống</v>
-      </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -514,10 +514,10 @@
         <v>Yêu cầu được gửi đi đúng cú pháp nhưng người dùng không có quyền truy cập vào tài nguyên này — lỗi phân quyền (Authorization)</v>
       </c>
       <c r="F4" t="str">
+        <v>Đường dẫn API (Endpoint URL) không tồn tại trên hệ thống máy chủ — lỗi không tìm thấy</v>
+      </c>
+      <c r="G4" t="str">
         <v>Người dùng chưa thực hiện đăng nhập tài khoản vào hệ thống — lỗi xác thực (Authentication)</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Đường dẫn API (Endpoint URL) không tồn tại trên hệ thống máy chủ — lỗi không tìm thấy</v>
       </c>
       <c r="H4" t="str">
         <v>Dữ liệu gửi lên vượt quá giới hạn dung lượng cho phép của server</v>
@@ -540,19 +540,19 @@
         <v>Locator (bộ định vị) giúp script tự động biết cần click vào nút nào, nhập chữ vào ô nào bằng cách quét cấu trúc DOM của trang web.</v>
       </c>
       <c r="E5" t="str">
-        <v>Định vị các phần tử giao diện (UI Elements) trên trang web để script tương tác click/type — ví dụ: ID, Name, XPath, CSS Selector</v>
+        <v>Xác định vị trí địa lý GPS của máy chủ lưu trữ mã nguồn kiểm thử</v>
       </c>
       <c r="F5" t="str">
-        <v>Xác định vị trí địa lý GPS của máy chủ lưu trữ mã nguồn kiểm thử</v>
+        <v>Tự động sinh ra các đoạn mã lập trình giao diện Frontend cho dự án</v>
       </c>
       <c r="G5" t="str">
         <v>Tính toán thời gian phản hồi trung bình của các API kết nối cơ sở dữ liệu</v>
       </c>
       <c r="H5" t="str">
-        <v>Tự động sinh ra các đoạn mã lập trình giao diện Frontend cho dự án</v>
+        <v>Định vị các phần tử giao diện (UI Elements) trên trang web để script tương tác click/type — ví dụ: ID, Name, XPath, CSS Selector</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -572,13 +572,13 @@
         <v>Viết mã JavaScript để tự động hóa việc xác thực kết quả trả về (Assertions) như kiểm tra Status Code, thời gian phản hồi, hoặc cấu trúc JSON</v>
       </c>
       <c r="F6" t="str">
+        <v>Xem lịch sử các request API đã được gửi đi trong quá khứ của tài khoản</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Cấu hình môi trường mạng proxy kết nối internet cho ứng dụng Postman</v>
+      </c>
+      <c r="H6" t="str">
         <v>Nhập các tham số đầu vào (Headers, Body) để gửi lên máy chủ API</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Xem lịch sử các request API đã được gửi đi trong quá khứ của tài khoản</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Cấu hình môi trường mạng proxy kết nối internet cho ứng dụng Postman</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -598,19 +598,19 @@
         <v>Tìm kiếm phần tử bằng ID luôn nhanh nhất và ổn định nhất vì ID được thiết kế là duy nhất trên trang, giúp script không bị nhận nhầm phần tử.</v>
       </c>
       <c r="E7" t="str">
+        <v>XPath Selector — do khả năng duyệt cây DOM phức tạp theo cả chiều dọc lẫn chiều ngang</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Class Name Selector — do class đại diện cho nhiều phần tử giao diện tương đồng</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Link Text Selector — do so khớp chuỗi chữ hiển thị trực tiếp của các thẻ liên kết</v>
+      </c>
+      <c r="H7" t="str">
         <v>ID Selector — do tính chất duy nhất của thuộc tính id trên trang web giúp trình duyệt tìm kiếm trực tiếp</v>
       </c>
-      <c r="F7" t="str">
-        <v>XPath Selector — do khả năng duyệt cây DOM phức tạp theo cả chiều dọc lẫn chiều ngang</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Class Name Selector — do class đại diện cho nhiều phần tử giao diện tương đồng</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Link Text Selector — do so khớp chuỗi chữ hiển thị trực tiếp của các thẻ liên kết</v>
-      </c>
       <c r="I7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -627,19 +627,19 @@
         <v>Selenium WebDriver đóng vai trò trung gian nhận lệnh từ script test và dịch thành các hành động điều khiển native trên trình duyệt web.</v>
       </c>
       <c r="E8" t="str">
+        <v>Quản lý và chỉnh sửa mã nguồn của lập trình viên Frontend trên server</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Thiết kế các kịch bản kiểm thử hiệu năng chịu tải tối đa của hệ thống API</v>
+      </c>
+      <c r="G8" t="str">
         <v>Cung cấp API điều khiển và tương tác trực tiếp với các trình duyệt web (Chrome, Firefox, Safari) như một người dùng thực tế</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Quản lý và chỉnh sửa mã nguồn của lập trình viên Frontend trên server</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Thiết kế các kịch bản kiểm thử hiệu năng chịu tải tối đa của hệ thống API</v>
       </c>
       <c r="H8" t="str">
         <v>Tự động phát hiện các lỗi bảo mật SQL Injection trong cơ sở dữ liệu</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -656,7 +656,7 @@
         <v>Theo chuẩn RESTful, PATCH dùng cho cập nhật cục bộ một số trường, trong khi PUT dùng để thay thế toàn bộ tài nguyên cũ bằng tài nguyên mới.</v>
       </c>
       <c r="E9" t="str">
-        <v>PATCH — cập nhật một phần thực thể dữ liệu (partial update)</v>
+        <v>POST — tạo mới hoàn toàn thực thể dữ liệu trên máy chủ</v>
       </c>
       <c r="F9" t="str">
         <v>PUT — cập nhật toàn bộ thực thể dữ liệu (replace update)</v>
@@ -665,10 +665,10 @@
         <v>GET — lấy thông tin thực thể dữ liệu về máy khách</v>
       </c>
       <c r="H9" t="str">
-        <v>POST — tạo mới hoàn toàn thực thể dữ liệu trên máy chủ</v>
+        <v>PATCH — cập nhật một phần thực thể dữ liệu (partial update)</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -685,19 +685,19 @@
         <v>401 (Authentication) yêu cầu xác định "Bạn là ai?". 403 (Authorization) kiểm tra "Bạn có quyền thực hiện việc này không?".</v>
       </c>
       <c r="E10" t="str">
+        <v>401 là lỗi do máy chủ Backend; 403 là lỗi do trình duyệt Frontend</v>
+      </c>
+      <c r="F10" t="str">
+        <v>401 báo lỗi đường dẫn sai; 403 báo lỗi cơ sở dữ liệu bị khóa tạm thời</v>
+      </c>
+      <c r="G10" t="str">
         <v>401 báo lỗi chưa xác thực danh tính (chưa đăng nhập); 403 báo lỗi không có quyền truy cập dù đã đăng nhập</v>
       </c>
-      <c r="F10" t="str">
-        <v>401 là lỗi do máy chủ Backend; 403 là lỗi do trình duyệt Frontend</v>
-      </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>401 chỉ xuất hiện khi gọi API GET; 403 chỉ xuất hiện khi gọi API POST</v>
       </c>
-      <c r="H10" t="str">
-        <v>401 báo lỗi đường dẫn sai; 403 báo lỗi cơ sở dữ liệu bị khóa tạm thời</v>
-      </c>
       <c r="I10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>Với phần tử động, QA sử dụng XPath tương đối, so khớp chuỗi con (`contains`) hoặc tìm theo quan hệ cha-con (relative XPath) để đảm bảo script chạy ổn định.</v>
       </c>
       <c r="E11" t="str">
+        <v>Dùng ID tĩnh bất kỳ tìm được ở lần F5 đầu tiên và chấp nhận script bị lỗi ở các lần chạy sau</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Chụp ảnh giao diện nút và dùng phần mềm nhận diện hình ảnh để script tự click chuột</v>
+      </c>
+      <c r="G11" t="str">
         <v>Dùng XPath/CSS Selector dựa trên các thuộc tính tương đối không đổi (ví dụ: `//button[contains(@class, 'btn-submit')]` hoặc `//button[text()='Lưu']`)</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Dùng ID tĩnh bất kỳ tìm được ở lần F5 đầu tiên và chấp nhận script bị lỗi ở các lần chạy sau</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Chụp ảnh giao diện nút và dùng phần mềm nhận diện hình ảnh để script tự click chuột</v>
       </c>
       <c r="H11" t="str">
         <v>Chờ lập trình viên sửa code để gán ID tĩnh mới tiến hành viết mã kiểm thử tự động</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -743,19 +743,19 @@
         <v>Implicit Wait cấu hình chung (global). Explicit Wait thông minh hơn, chỉ kích hoạt khi cần thiết (ví dụ: Chờ nút hiển thị rõ để click - ExpectedConditions) giúp giảm flaky test.</v>
       </c>
       <c r="E12" t="str">
+        <v>Implicit Wait chỉ chạy trên trình duyệt Chrome; Explicit Wait chạy trên mọi trình duyệt</v>
+      </c>
+      <c r="F12" t="str">
         <v>Implicit Wait áp dụng thời gian chờ mặc định cho mọi phần tử trong suốt session; Explicit Wait cấu hình chờ cho một phần tử cụ thể thỏa mãn điều kiện chỉ định</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
+        <v>Implicit Wait làm chậm tốc độ chạy script; Explicit Wait tăng tốc độ chạy script lên tối đa</v>
+      </c>
+      <c r="H12" t="str">
         <v>Implicit Wait chờ đến khi trang tải xong 100%; Explicit Wait chỉ chờ các đoạn mã JavaScript chạy xong</v>
       </c>
-      <c r="G12" t="str">
-        <v>Implicit Wait chỉ chạy trên trình duyệt Chrome; Explicit Wait chạy trên mọi trình duyệt</v>
-      </c>
-      <c r="H12" t="str">
-        <v>Implicit Wait làm chậm tốc độ chạy script; Explicit Wait tăng tốc độ chạy script lên tối đa</v>
-      </c>
       <c r="I12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -772,7 +772,7 @@
         <v>POM đóng gói các phần tử và hành vi của một trang web vào một Class. Khi giao diện đổi (ví dụ đổi ID của nút), QA chỉ cần sửa Locator trong Class Page đó, không phải sửa hàng chục Test script.</v>
       </c>
       <c r="E13" t="str">
-        <v>Tách biệt mã nguồn tương tác giao diện và mã nguồn kịch bản kiểm thử; giúp dễ bảo trì, tái sử dụng code và giảm thiểu công sức sửa script khi UI thay đổi</v>
+        <v>Đảm bảo không phát sinh bất kỳ lỗi flaky test nào trong suốt quá trình chạy kịch bản</v>
       </c>
       <c r="F13" t="str">
         <v>Tăng tốc độ thực thi các ca kiểm thử tự động lên gấp nhiều lần trên máy chủ</v>
@@ -781,10 +781,10 @@
         <v>Tự động hóa hoàn toàn việc viết các test case mà không cần QA phải tự tay viết code</v>
       </c>
       <c r="H13" t="str">
-        <v>Đảm bảo không phát sinh bất kỳ lỗi flaky test nào trong suốt quá trình chạy kịch bản</v>
+        <v>Tách biệt mã nguồn tương tác giao diện và mã nguồn kịch bản kiểm thử; giúp dễ bảo trì, tái sử dụng code và giảm thiểu công sức sửa script khi UI thay đổi</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         <v>Sử dụng biến môi trường (e.g. `pm.environment.set("token", pm.response.json().token)`) giúp tự động hóa hoàn toàn chuỗi API test chain.</v>
       </c>
       <c r="E14" t="str">
+        <v>Copy thủ công token bằng tay và paste vào từng request API trước mỗi lần chạy test</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Lưu token vào một file text trên máy tính cá nhân và yêu cầu Postman tự đọc file đó</v>
+      </c>
+      <c r="G14" t="str">
         <v>Viết mã JavaScript trong tab "Tests" của API Đăng nhập để lưu token vào biến môi trường (Environment Variable), sau đó gọi biến này trong Authorization header của các API tiếp theo</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Copy thủ công token bằng tay và paste vào từng request API trước mỗi lần chạy test</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Lưu token vào một file text trên máy tính cá nhân và yêu cầu Postman tự đọc file đó</v>
       </c>
       <c r="H14" t="str">
         <v>Không cần làm gì vì Postman tự động nhận diện và chia sẻ token bảo mật giữa các API</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -833,13 +833,13 @@
         <v>Phần tử giao diện đã từng được tìm thấy nhưng hiện tại không còn tồn tại trong cây DOM của trang web (do trang đã reload hoặc cập nhật AJAX)</v>
       </c>
       <c r="F15" t="str">
-        <v>Trình duyệt web bị tắt đột ngột do thiếu bộ nhớ RAM trên máy tính chạy test</v>
+        <v>Tài khoản đăng nhập trên trình duyệt đã bị hết hạn phiên làm việc (session timeout)</v>
       </c>
       <c r="G15" t="str">
         <v>Đoạn script test tự động chứa lỗi cú pháp lập trình không thể biên dịch</v>
       </c>
       <c r="H15" t="str">
-        <v>Tài khoản đăng nhập trên trình duyệt đã bị hết hạn phiên làm việc (session timeout)</v>
+        <v>Trình duyệt web bị tắt đột ngột do thiếu bộ nhớ RAM trên máy tính chạy test</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -859,19 +859,19 @@
         <v>SOAP là giao thức đặc tả chặt chẽ dựa trên XML. REST là phong cách kiến trúc nhẹ nhàng, dễ sử dụng, được ứng dụng rộng rãi trong các ứng dụng web/mobile hiện đại.</v>
       </c>
       <c r="E16" t="str">
+        <v>SOAP là phiên bản mới hơn và đang dần thay thế hoàn toàn REST trên thị trường</v>
+      </c>
+      <c r="F16" t="str">
+        <v>SOAP chỉ chạy trên môi trường di động; REST chỉ chạy trên trình duyệt máy tính</v>
+      </c>
+      <c r="G16" t="str">
+        <v>SOAP chạy nhanh hơn REST gấp nhiều lần vì nó không sử dụng giao thức bảo mật</v>
+      </c>
+      <c r="H16" t="str">
         <v>SOAP bắt buộc sử dụng định dạng XML và có giao thức nghiêm ngặt (WSDL); REST linh hoạt hỗ trợ nhiều định dạng (thường là JSON) và dựa trên các phương thức HTTP tiêu chuẩn</v>
       </c>
-      <c r="F16" t="str">
-        <v>SOAP chạy nhanh hơn REST gấp nhiều lần vì nó không sử dụng giao thức bảo mật</v>
-      </c>
-      <c r="G16" t="str">
-        <v>SOAP chỉ chạy trên môi trường di động; REST chỉ chạy trên trình duyệt máy tính</v>
-      </c>
-      <c r="H16" t="str">
-        <v>SOAP là phiên bản mới hơn và đang dần thay thế hoàn toàn REST trên thị trường</v>
-      </c>
       <c r="I16">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -888,19 +888,19 @@
         <v>Data-driven testing giúp tăng độ bao phủ. Thay vì viết 10 test case riêng biệt cho 10 tài khoản, ta chỉ viết 1 script và nạp 10 dòng tài khoản từ file CSV vào.</v>
       </c>
       <c r="E17" t="str">
+        <v>Tự động tối ưu hóa tốc độ truy vấn của cơ sở dữ liệu quan hệ trong quá trình chạy test</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Tự động mã hóa toàn bộ dữ liệu nhạy cảm của người dùng trong cơ sở dữ liệu</v>
+      </c>
+      <c r="G17" t="str">
         <v>Chạy một kịch bản kiểm thử nhiều lần với các bộ dữ liệu đầu vào và kết quả mong đợi khác nhau đọc từ file ngoài (CSV, Excel, JSON)</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Tự động tối ưu hóa tốc độ truy vấn của cơ sở dữ liệu quan hệ trong quá trình chạy test</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Tự động mã hóa toàn bộ dữ liệu nhạy cảm của người dùng trong cơ sở dữ liệu</v>
       </c>
       <c r="H17" t="str">
         <v>Xác định số lượng máy chủ ảo cần thiết để chạy song song các kịch bản kiểm thử</v>
       </c>
       <c r="I17">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -920,13 +920,13 @@
         <v>`/` tìm kiếm phần tử con trực tiếp (absolute path); `//` tìm kiếm phần tử con ở bất kỳ cấp độ nào bên trong (relative path)</v>
       </c>
       <c r="F18" t="str">
+        <v>`/` tìm kiếm theo ID; `//` tìm kiếm theo Class Name của phần tử</v>
+      </c>
+      <c r="G18" t="str">
+        <v>`/` chạy nhanh hơn `//` gấp 10 lần trong mọi cấu trúc trang web</v>
+      </c>
+      <c r="H18" t="str">
         <v>`/` chỉ dùng ở đầu câu lệnh; `//` chỉ dùng ở cuối câu lệnh XPath</v>
-      </c>
-      <c r="G18" t="str">
-        <v>`/` tìm kiếm theo ID; `//` tìm kiếm theo Class Name của phần tử</v>
-      </c>
-      <c r="H18" t="str">
-        <v>`/` chạy nhanh hơn `//` gấp 10 lần trong mọi cấu trúc trang web</v>
       </c>
       <c r="I18">
         <v>1</v>
@@ -975,19 +975,19 @@
         <v>Lỗi này do phần tử bị che bởi một phần tử khác (như spinner, popup quảng cáo). Cách sạch nhất là chờ spinner biến mất, hoặc dùng JS click `arguments[0].click();` để tác động thẳng vào DOM.</v>
       </c>
       <c r="E20" t="str">
+        <v>Chuyển sang chạy script trên một trình duyệt khác ít bảo mật hơn (ví dụ: Internet Explorer)</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Báo cáo lỗi cho dev yêu cầu gỡ bỏ toàn bộ CSS hiệu ứng chuyển động của trang web</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Tăng thời gian Thread.sleep() lên 10 giây trước mỗi hành động click chuột của script</v>
+      </c>
+      <c r="H20" t="str">
         <v>Sử dụng Explicit Wait để chờ phần tử che khuất biến mất (ví dụ: loading spinner), hoặc dùng JavascriptExecutor để click trực tiếp vào phần tử bỏ qua lớp che phủ DOM</v>
       </c>
-      <c r="F20" t="str">
-        <v>Tăng thời gian Thread.sleep() lên 10 giây trước mỗi hành động click chuột của script</v>
-      </c>
-      <c r="G20" t="str">
-        <v>Chuyển sang chạy script trên một trình duyệt khác ít bảo mật hơn (ví dụ: Internet Explorer)</v>
-      </c>
-      <c r="H20" t="str">
-        <v>Báo cáo lỗi cho dev yêu cầu gỡ bỏ toàn bộ CSS hiệu ứng chuyển động của trang web</v>
-      </c>
       <c r="I20">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1004,19 +1004,19 @@
         <v>Hệ thống cần validate kiểu dữ liệu ở tầng API/Controller và trả về lỗi 4xx rõ ràng. Việc trả về lỗi 500 kèm SQL dump chứng tỏ BE để lọt dữ liệu bẩn xuống DB, gây nguy cơ bảo mật nghiêm trọng.</v>
       </c>
       <c r="E21" t="str">
+        <v>Lỗi mạng kết nối giữa Postman và máy chủ API bị chập chờn khi truyền chuỗi ký tự</v>
+      </c>
+      <c r="F21" t="str">
         <v>Lỗi Backend thiếu cơ chế validate dữ liệu đầu vào và thiếu try-catch bắt lỗi hệ thống — làm lộ chi tiết truy vấn DB (SQL exception) gây rủi ro bảo mật (SQL Injection)</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Lỗi Database bị crash do kiểu dữ liệu của ID quá dài không thể xử lý được ở mức vật lý</v>
       </c>
       <c r="G21" t="str">
         <v>Hành vi đúng của hệ thống vì nhập sai kiểu dữ liệu thì server bắt buộc phải báo lỗi 500</v>
       </c>
       <c r="H21" t="str">
-        <v>Lỗi mạng kết nối giữa Postman và máy chủ API bị chập chờn khi truyền chuỗi ký tự</v>
+        <v>Lỗi Database bị crash do kiểu dữ liệu của ID quá dài không thể xử lý được ở mức vật lý</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1033,19 +1033,19 @@
         <v>Factory Pattern giúp quản lý việc tạo đối tượng Page. Khi chuyển trang, Factory tự động sinh ra Page Object tiếp theo tương ứng, giữ cho mã nguồn script gọn gàng và dễ mở rộng.</v>
       </c>
       <c r="E22" t="str">
+        <v>Để tăng tốc độ biên dịch mã nguồn của script test tự động từ Java sang NodeJS</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Để script tự động tìm kiếm các locator thay thế khi locator chính bị hỏng trên giao diện</v>
+      </c>
+      <c r="G22" t="str">
         <v>Để tự động hóa việc khởi tạo các Page Object tương ứng với trạng thái hoạt động của trình duyệt, tránh việc khởi tạo thủ công lặp lại trong mã nguồn test</v>
       </c>
-      <c r="F22" t="str">
-        <v>Để tăng tốc độ biên dịch mã nguồn của script test tự động từ Java sang NodeJS</v>
-      </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <v>Để đảm bảo cơ sở dữ liệu tự động đồng bộ hóa dữ liệu test trước mỗi lần chạy kịch bản</v>
       </c>
-      <c r="H22" t="str">
-        <v>Để script tự động tìm kiếm các locator thay thế khi locator chính bị hỏng trên giao diện</v>
-      </c>
       <c r="I22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1062,19 +1062,19 @@
         <v>Cả hai kịch bản (Signature manipulation và Algorithm None attack) là các lỗ hổng kinh điển của JWT. Việc kiểm thử này giúp bảo vệ hệ thống trước các cuộc tấn công giả mạo danh tính.</v>
       </c>
       <c r="E23" t="str">
+        <v>Cả hai kịch bản trên đều cực kỳ quan trọng để đảm bảo tính xác thực và bảo mật của JWT</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Chỉ cần kiểm tra xem JWT có chứa thông tin mật khẩu thô của người dùng hay không</v>
+      </c>
+      <c r="G23" t="str">
         <v>Thử sửa đổi Signature của JWT gửi lên xem API có từ chối (401/403); thử gửi token đã hết hạn (expired token) xem hệ thống có chặn hay không</v>
       </c>
-      <c r="F23" t="str">
+      <c r="H23" t="str">
         <v>Thử đổi tên thuật toán mã hóa trong header của JWT sang "none" xem server có chấp nhận token không có chữ ký hay không</v>
       </c>
-      <c r="G23" t="str">
-        <v>Cả hai kịch bản trên đều cực kỳ quan trọng để đảm bảo tính xác thực và bảo mật của JWT</v>
-      </c>
-      <c r="H23" t="str">
-        <v>Chỉ cần kiểm tra xem JWT có chứa thông tin mật khẩu thô của người dùng hay không</v>
-      </c>
       <c r="I23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1091,19 +1091,19 @@
         <v>Chạy song song yêu cầu các test case không được dùng chung dữ liệu tĩnh (như dùng chung một tài khoản VIP để sửa thông tin cùng lúc). Thiết kế dữ liệu cô lập (Isolate) là nguyên tắc sống còn.</v>
       </c>
       <c r="E24" t="str">
+        <v>Tắt tính năng chạy song song và chuyển về chạy tuần tự từng test case một như cũ</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Tăng dung lượng CPU của máy chủ CI/CD chạy test tự động lên tối đa để xử lý tranh chấp</v>
+      </c>
+      <c r="G24" t="str">
         <v>Đảm bảo tính cô lập của dữ liệu (Data Isolation): Mỗi luồng chạy test sử dụng một bộ tài khoản/dữ liệu độc lập hoàn toàn, hoặc sử dụng các hàm sinh dữ liệu ngẫu nhiên (dynamic test data)</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Tắt tính năng chạy song song và chuyển về chạy tuần tự từng test case một như cũ</v>
-      </c>
-      <c r="G24" t="str">
-        <v>Tăng dung lượng CPU của máy chủ CI/CD chạy test tự động lên tối đa để xử lý tranh chấp</v>
       </c>
       <c r="H24" t="str">
         <v>Yêu cầu lập trình viên tạm thời khóa tính năng ghi dữ liệu của cơ sở dữ liệu khi chạy test</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1120,19 +1120,19 @@
         <v>Sử dụng AJV giúp QA validate toàn bộ cấu trúc response (kiểu dữ liệu, các trường bắt buộc, min/max length) chỉ bằng một đoạn code ngắn, đảm bảo API không bị đổi cấu trúc đột ngột.</v>
       </c>
       <c r="E25" t="str">
+        <v>Postman tự động validate JSON Schema ở mọi request mà không cần viết script</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Yêu cầu Backend cung cấp file WSDL để Postman tự động so khớp cấu trúc dữ liệu</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Viết nhiều câu lệnh `pm.expect` thủ công để so sánh từng trường dữ liệu một cách độc lập</v>
+      </c>
+      <c r="H25" t="str">
         <v>Sử dụng thư viện AJV (Another JSON Schema Validator) tích hợp sẵn trong Postman thông qua tab Tests để viết đoạn code validate schema</v>
       </c>
-      <c r="F25" t="str">
-        <v>Viết nhiều câu lệnh `pm.expect` thủ công để so sánh từng trường dữ liệu một cách độc lập</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Postman tự động validate JSON Schema ở mọi request mà không cần viết script</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Yêu cầu Backend cung cấp file WSDL để Postman tự động so khớp cấu trúc dữ liệu</v>
-      </c>
       <c r="I25">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1152,13 +1152,13 @@
         <v>Do thiết bị di động có tài nguyên giới hạn và dễ bị gián đoạn hệ thống (cuộc gọi, mất sóng). Giải pháp: Sử dụng các lệnh điều khiển hệ thống của Appium (ví dụ: `driver.backgroundApp()`, `driver.setConnection()`) để mô phỏng</v>
       </c>
       <c r="F26" t="str">
+        <v>Do Appium yêu cầu kết nối trực tiếp vào cáp quang của nhà mạng di động để truyền tải tập lệnh</v>
+      </c>
+      <c r="G26" t="str">
         <v>Do Appium không hỗ trợ chạy trên hệ điều hành Android. Giải pháp: Chỉ test trên giả lập iOS</v>
       </c>
-      <c r="G26" t="str">
+      <c r="H26" t="str">
         <v>Do ứng dụng di động tự động mã hóa mọi locator trên giao diện. Giải pháp: Sử dụng tọa độ pixel tĩnh để click chuột</v>
-      </c>
-      <c r="H26" t="str">
-        <v>Do Appium yêu cầu kết nối trực tiếp vào cáp quang của nhà mạng di động để truyền tải tập lệnh</v>
       </c>
       <c r="I26">
         <v>1</v>
